--- a/exodus/csv/Rescaling.xlsx
+++ b/exodus/csv/Rescaling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="17800" yWindow="600" windowWidth="28340" windowHeight="16260" tabRatio="500"/>
+    <workbookView xWindow="460" yWindow="600" windowWidth="28340" windowHeight="16260" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1786,7 +1786,7 @@
         <v>48.87</v>
       </c>
       <c r="E15">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1800,8 +1800,11 @@
         <f t="shared" si="0"/>
         <v>48.81</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1998</v>
       </c>
@@ -1812,8 +1815,11 @@
         <f t="shared" si="0"/>
         <v>48.61</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1999</v>
       </c>
@@ -1824,8 +1830,11 @@
         <f t="shared" si="0"/>
         <v>47.58</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2000</v>
       </c>
@@ -1836,8 +1845,11 @@
         <f t="shared" si="0"/>
         <v>65.52</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2001</v>
       </c>
@@ -1848,8 +1860,11 @@
         <f t="shared" si="0"/>
         <v>69.260000000000005</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2002</v>
       </c>
@@ -1860,8 +1875,11 @@
         <f t="shared" si="0"/>
         <v>45.42</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2003</v>
       </c>
@@ -1873,7 +1891,7 @@
         <v>38.380000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2004</v>
       </c>
@@ -1885,7 +1903,7 @@
         <v>43.55</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2005</v>
       </c>
@@ -1897,7 +1915,7 @@
         <v>38.93</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2006</v>
       </c>
@@ -1909,7 +1927,7 @@
         <v>37.840000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2007</v>
       </c>
@@ -1921,7 +1939,7 @@
         <v>55.85</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2008</v>
       </c>
@@ -1933,7 +1951,7 @@
         <v>51.66</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2009</v>
       </c>
@@ -1945,7 +1963,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2010</v>
       </c>
@@ -1957,7 +1975,7 @@
         <v>55.72</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2011</v>
       </c>
@@ -1969,7 +1987,7 @@
         <v>48.09</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2012</v>
       </c>
@@ -1981,7 +1999,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2013</v>
       </c>
